--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487879_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487879_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>1.9998</v>
+        <v>2.4196</v>
       </c>
       <c r="E2" t="n">
-        <v>3.7831</v>
+        <v>3.9974</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.7833</v>
+        <v>-1.5778</v>
       </c>
       <c r="G2" t="n">
         <v>6.5559</v>
@@ -610,13 +610,13 @@
         <v>1.8731</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.8912</v>
+        <v>-0.4714</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.2519</v>
+        <v>-0.0376</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.6393</v>
+        <v>-0.4338</v>
       </c>
       <c r="V2" t="n">
         <v>-1.1675</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A. ALFAMA AMADO</t>
+          <t>P. FERNANDEZ CHOCARRO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.0119</v>
+        <v>-0.3762</v>
       </c>
       <c r="E3" t="n">
-        <v>2.0961</v>
+        <v>-0.2244</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.0842</v>
+        <v>-0.1518</v>
       </c>
       <c r="G3" t="n">
-        <v>0.9546</v>
+        <v>0.2298</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1276</v>
+        <v>1.0087</v>
       </c>
       <c r="I3" t="n">
-        <v>0.827</v>
+        <v>-0.7789</v>
       </c>
       <c r="J3" t="n">
-        <v>1.5876</v>
+        <v>-0.1172</v>
       </c>
       <c r="K3" t="n">
-        <v>0.7647</v>
+        <v>0.0576</v>
       </c>
       <c r="L3" t="n">
-        <v>0.823</v>
+        <v>-0.1747</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.633</v>
+        <v>0.347</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.6371</v>
+        <v>0.9510999999999999</v>
       </c>
       <c r="O3" t="n">
-        <v>0.0041</v>
+        <v>-0.6041</v>
       </c>
       <c r="P3" t="n">
-        <v>-1.4568</v>
+        <v>1.0406</v>
       </c>
       <c r="Q3" t="n">
-        <v>-3.3299</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1.8731</v>
+        <v>1.0406</v>
       </c>
       <c r="S3" t="n">
-        <v>3.8492</v>
+        <v>-0.709</v>
       </c>
       <c r="T3" t="n">
-        <v>2.6709</v>
+        <v>-0.3372</v>
       </c>
       <c r="U3" t="n">
-        <v>1.1783</v>
+        <v>-0.3718</v>
       </c>
       <c r="V3" t="n">
-        <v>-2.3351</v>
+        <v>-0.9376</v>
       </c>
       <c r="W3" t="n">
-        <v>1.1675</v>
+        <v>0.23</v>
       </c>
       <c r="X3" t="n">
-        <v>-3.5026</v>
+        <v>-1.1675</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>P. FERNANDEZ CHOCARRO</t>
+          <t>P. YARNOZ LUMBRERAS</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.6888</v>
+        <v>-0.9520999999999999</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.3315</v>
+        <v>0.9519</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.3573</v>
+        <v>-1.904</v>
       </c>
       <c r="G4" t="n">
-        <v>0.2298</v>
+        <v>0.5054</v>
       </c>
       <c r="H4" t="n">
-        <v>1.0087</v>
+        <v>1.1324</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.7789</v>
+        <v>-0.627</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.1172</v>
+        <v>1.1465</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0576</v>
+        <v>1.2428</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.1747</v>
+        <v>-0.0963</v>
       </c>
       <c r="M4" t="n">
-        <v>0.347</v>
+        <v>-0.6411</v>
       </c>
       <c r="N4" t="n">
-        <v>0.9510999999999999</v>
+        <v>-0.1105</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.6041</v>
+        <v>-0.5306999999999999</v>
       </c>
       <c r="P4" t="n">
-        <v>1.0406</v>
+        <v>-1.0406</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-2.2893</v>
       </c>
       <c r="R4" t="n">
-        <v>1.0406</v>
+        <v>1.2487</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.0217</v>
+        <v>0.3968</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.4443</v>
+        <v>0.4672</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.5774</v>
+        <v>-0.0704</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.9376</v>
+        <v>-0.8137</v>
       </c>
       <c r="W4" t="n">
-        <v>0.23</v>
+        <v>1.6275</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.1675</v>
+        <v>-2.4412</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>P. YARNOZ LUMBRERAS</t>
+          <t>A. ALFAMA AMADO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.9536</v>
+        <v>-1.2795</v>
       </c>
       <c r="E5" t="n">
-        <v>1.2733</v>
+        <v>0.2745</v>
       </c>
       <c r="F5" t="n">
-        <v>-2.227</v>
+        <v>-1.5539</v>
       </c>
       <c r="G5" t="n">
-        <v>0.5054</v>
+        <v>0.9546</v>
       </c>
       <c r="H5" t="n">
-        <v>1.1324</v>
+        <v>0.1276</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.627</v>
+        <v>0.827</v>
       </c>
       <c r="J5" t="n">
-        <v>1.1465</v>
+        <v>1.5876</v>
       </c>
       <c r="K5" t="n">
-        <v>1.2428</v>
+        <v>0.7647</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.0963</v>
+        <v>0.823</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.6411</v>
+        <v>-0.633</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.1105</v>
+        <v>-0.6371</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.5306999999999999</v>
+        <v>0.0041</v>
       </c>
       <c r="P5" t="n">
-        <v>-1.0406</v>
+        <v>-1.4568</v>
       </c>
       <c r="Q5" t="n">
-        <v>-2.2893</v>
+        <v>-3.3299</v>
       </c>
       <c r="R5" t="n">
-        <v>1.2487</v>
+        <v>1.8731</v>
       </c>
       <c r="S5" t="n">
-        <v>0.3953</v>
+        <v>1.5578</v>
       </c>
       <c r="T5" t="n">
-        <v>0.7887</v>
+        <v>0.8492</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.3934</v>
+        <v>0.7086</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.8137</v>
+        <v>-2.3351</v>
       </c>
       <c r="W5" t="n">
-        <v>1.6275</v>
+        <v>1.1675</v>
       </c>
       <c r="X5" t="n">
-        <v>-2.4412</v>
+        <v>-3.5026</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>W. BURGOS CABRERA</t>
+          <t>A. CALVO TORRES</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.1891</v>
+        <v>-1.3535</v>
       </c>
       <c r="E6" t="n">
-        <v>-2.399</v>
+        <v>-1.2095</v>
       </c>
       <c r="F6" t="n">
-        <v>1.2099</v>
+        <v>-0.144</v>
       </c>
       <c r="G6" t="n">
-        <v>-2.0052</v>
+        <v>-0.4659</v>
       </c>
       <c r="H6" t="n">
-        <v>0.1984</v>
+        <v>-0.083</v>
       </c>
       <c r="I6" t="n">
-        <v>-2.2035</v>
+        <v>-0.3829</v>
       </c>
       <c r="J6" t="n">
-        <v>-1.9112</v>
+        <v>0.0363</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.5609</v>
+        <v>-0.5033</v>
       </c>
       <c r="L6" t="n">
-        <v>-1.3504</v>
+        <v>0.5396</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.0939</v>
+        <v>-0.5022</v>
       </c>
       <c r="N6" t="n">
-        <v>0.7592</v>
+        <v>0.4203</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.8532</v>
+        <v>-0.9225</v>
       </c>
       <c r="P6" t="n">
-        <v>0.6244</v>
+        <v>-0.6244</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-1.0406</v>
       </c>
       <c r="R6" t="n">
-        <v>0.6244</v>
+        <v>0.4162</v>
       </c>
       <c r="S6" t="n">
-        <v>0.0679</v>
+        <v>-0.2632</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.7177</v>
+        <v>-0.2052</v>
       </c>
       <c r="U6" t="n">
-        <v>0.7856</v>
+        <v>-0.058</v>
       </c>
       <c r="V6" t="n">
-        <v>0.1238</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>0.23</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.1061</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. CALVO TORRES</t>
+          <t>W. BURGOS CABRERA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-2.4368</v>
+        <v>-1.3858</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.8524</v>
+        <v>-2.1846</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.5844</v>
+        <v>0.7988</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.4659</v>
+        <v>-2.0052</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.083</v>
+        <v>0.1984</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.3829</v>
+        <v>-2.2035</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0363</v>
+        <v>-1.9112</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.5033</v>
+        <v>-0.5609</v>
       </c>
       <c r="L7" t="n">
-        <v>0.5396</v>
+        <v>-1.3504</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.5022</v>
+        <v>-0.0939</v>
       </c>
       <c r="N7" t="n">
-        <v>0.4203</v>
+        <v>0.7592</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.9225</v>
+        <v>-0.8532</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.6244</v>
+        <v>0.6244</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.0406</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0.4162</v>
+        <v>0.6244</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.3466</v>
+        <v>-0.1288</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.8482</v>
+        <v>-0.5034</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.4984</v>
+        <v>0.3745</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>0.1238</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>0.23</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-0.1061</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. KNOTEK</t>
+          <t>F. SANTANA ROSALES</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.9517</v>
+        <v>-2.9081</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.5716</v>
+        <v>-1.4732</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.3802</v>
+        <v>-1.4349</v>
       </c>
       <c r="G8" t="n">
-        <v>-3.8368</v>
+        <v>-1.7926</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.8978</v>
+        <v>0.5995</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.939</v>
+        <v>-2.3921</v>
       </c>
       <c r="J8" t="n">
-        <v>-1.1545</v>
+        <v>0.0569</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.6361</v>
+        <v>1.6694</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.5184</v>
+        <v>-1.6125</v>
       </c>
       <c r="M8" t="n">
-        <v>-2.6823</v>
+        <v>-1.8495</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.2617</v>
+        <v>-1.0699</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.4206</v>
+        <v>-0.7796999999999999</v>
       </c>
       <c r="P8" t="n">
-        <v>-1.0406</v>
+        <v>0.4162</v>
       </c>
       <c r="Q8" t="n">
-        <v>-2.2893</v>
+        <v>-1.2487</v>
       </c>
       <c r="R8" t="n">
-        <v>1.2487</v>
+        <v>1.6649</v>
       </c>
       <c r="S8" t="n">
-        <v>0.7581</v>
+        <v>-0.3642</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.5252</v>
+        <v>-0.2814</v>
       </c>
       <c r="U8" t="n">
-        <v>1.2834</v>
+        <v>-0.0828</v>
       </c>
       <c r="V8" t="n">
-        <v>1.1675</v>
+        <v>-1.1675</v>
       </c>
       <c r="W8" t="n">
-        <v>1.3975</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.23</v>
+        <v>-1.1675</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>F. SANTANA ROSALES</t>
+          <t>J. KNOTEK</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.8637</v>
+        <v>-3.1103</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.2233</v>
+        <v>-2.1429</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.6404</v>
+        <v>-0.9674</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.7926</v>
+        <v>-3.8368</v>
       </c>
       <c r="H9" t="n">
-        <v>0.5995</v>
+        <v>-1.8978</v>
       </c>
       <c r="I9" t="n">
-        <v>-2.3921</v>
+        <v>-1.939</v>
       </c>
       <c r="J9" t="n">
-        <v>0.0569</v>
+        <v>-1.1545</v>
       </c>
       <c r="K9" t="n">
-        <v>1.6694</v>
+        <v>-0.6361</v>
       </c>
       <c r="L9" t="n">
-        <v>-1.6125</v>
+        <v>-0.5184</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.8495</v>
+        <v>-2.6823</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.0699</v>
+        <v>-1.2617</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.7796999999999999</v>
+        <v>-1.4206</v>
       </c>
       <c r="P9" t="n">
-        <v>0.4162</v>
+        <v>-1.0406</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.2487</v>
+        <v>-2.2893</v>
       </c>
       <c r="R9" t="n">
-        <v>1.6649</v>
+        <v>1.2487</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.3198</v>
+        <v>0.5996</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.0315</v>
+        <v>-0.09660000000000001</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.2883</v>
+        <v>0.6962</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.1675</v>
+        <v>1.1675</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.3975</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.1675</v>
+        <v>-0.23</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-5.404</v>
+        <v>-5.5303</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.47</v>
+        <v>-3.6843</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.9341</v>
+        <v>-1.846</v>
       </c>
       <c r="G10" t="n">
         <v>-2.8596</v>
@@ -1234,13 +1234,13 @@
         <v>0.4162</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.8794999999999999</v>
+        <v>-1.0057</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.2643</v>
+        <v>-0.4786</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.6152</v>
+        <v>-0.5271</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1267,31 +1267,31 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-14.476</v>
+        <v>-14.4762</v>
       </c>
       <c r="E11" t="n">
-        <v>-5.695300000000001</v>
+        <v>-5.6951</v>
       </c>
       <c r="F11" t="n">
         <v>-8.781000000000001</v>
       </c>
       <c r="G11" t="n">
-        <v>-2.714399999999999</v>
+        <v>-2.714400000000001</v>
       </c>
       <c r="H11" t="n">
-        <v>3.3477</v>
+        <v>3.347699999999999</v>
       </c>
       <c r="I11" t="n">
         <v>-6.062</v>
       </c>
       <c r="J11" t="n">
-        <v>5.7578</v>
+        <v>5.757799999999999</v>
       </c>
       <c r="K11" t="n">
-        <v>5.6151</v>
+        <v>5.615099999999999</v>
       </c>
       <c r="L11" t="n">
-        <v>0.1427999999999999</v>
+        <v>0.1427999999999995</v>
       </c>
       <c r="M11" t="n">
         <v>-8.472100000000001</v>
@@ -1312,13 +1312,13 @@
         <v>10.4059</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.3883000000000001</v>
+        <v>-0.3880999999999999</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.6235000000000004</v>
+        <v>-0.6235999999999998</v>
       </c>
       <c r="U11" t="n">
-        <v>0.2352999999999998</v>
+        <v>0.2353999999999999</v>
       </c>
       <c r="V11" t="n">
         <v>-5.1301</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>6.1029</v>
+        <v>6.1704</v>
       </c>
       <c r="E12" t="n">
-        <v>4.9336</v>
+        <v>5.1479</v>
       </c>
       <c r="F12" t="n">
-        <v>1.1693</v>
+        <v>1.0225</v>
       </c>
       <c r="G12" t="n">
         <v>4.3562</v>
@@ -1390,13 +1390,13 @@
         <v>2.0812</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.0045</v>
+        <v>0.063</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.3543</v>
+        <v>-0.14</v>
       </c>
       <c r="U12" t="n">
-        <v>0.3498</v>
+        <v>0.203</v>
       </c>
       <c r="V12" t="n">
         <v>1.7513</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>5.7359</v>
+        <v>5.4335</v>
       </c>
       <c r="E13" t="n">
-        <v>3.4904</v>
+        <v>3.2761</v>
       </c>
       <c r="F13" t="n">
-        <v>2.2455</v>
+        <v>2.1574</v>
       </c>
       <c r="G13" t="n">
         <v>1.2479</v>
@@ -1468,13 +1468,13 @@
         <v>1.6649</v>
       </c>
       <c r="S13" t="n">
-        <v>0.488</v>
+        <v>0.1856</v>
       </c>
       <c r="T13" t="n">
-        <v>0.09909999999999999</v>
+        <v>-0.1152</v>
       </c>
       <c r="U13" t="n">
-        <v>0.3889</v>
+        <v>0.3008</v>
       </c>
       <c r="V13" t="n">
         <v>2.3351</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.7512</v>
+        <v>2.8235</v>
       </c>
       <c r="E14" t="n">
-        <v>3.3283</v>
+        <v>2.8997</v>
       </c>
       <c r="F14" t="n">
-        <v>0.4229</v>
+        <v>-0.0762</v>
       </c>
       <c r="G14" t="n">
         <v>1.4838</v>
@@ -1546,13 +1546,13 @@
         <v>2.2893</v>
       </c>
       <c r="S14" t="n">
-        <v>1.8294</v>
+        <v>0.9016</v>
       </c>
       <c r="T14" t="n">
-        <v>0.7358</v>
+        <v>0.3072</v>
       </c>
       <c r="U14" t="n">
-        <v>1.0935</v>
+        <v>0.5944</v>
       </c>
       <c r="V14" t="n">
         <v>0.23</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A. MORALES ROS</t>
+          <t>J. CERA RODRIGUEZ</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.5406</v>
+        <v>1.4649</v>
       </c>
       <c r="E15" t="n">
-        <v>0.9009</v>
+        <v>2.0053</v>
       </c>
       <c r="F15" t="n">
-        <v>0.6397</v>
+        <v>-0.5404</v>
       </c>
       <c r="G15" t="n">
-        <v>0.5607</v>
+        <v>1.8423</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.4304</v>
+        <v>0.0511</v>
       </c>
       <c r="I15" t="n">
-        <v>0.9911</v>
+        <v>1.7912</v>
       </c>
       <c r="J15" t="n">
-        <v>1.3202</v>
+        <v>2.9937</v>
       </c>
       <c r="K15" t="n">
-        <v>0.1535</v>
+        <v>0.7779</v>
       </c>
       <c r="L15" t="n">
-        <v>1.1667</v>
+        <v>2.2158</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.7595</v>
+        <v>-1.1513</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.5839</v>
+        <v>-0.7268</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.1755</v>
+        <v>-0.4245</v>
       </c>
       <c r="P15" t="n">
-        <v>0.8325</v>
+        <v>-0.4162</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.0406</v>
+        <v>-2.0812</v>
       </c>
       <c r="R15" t="n">
-        <v>1.8731</v>
+        <v>1.6649</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.3125</v>
+        <v>0.0388</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.06850000000000001</v>
+        <v>-0.0747</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.244</v>
+        <v>0.1136</v>
       </c>
       <c r="V15" t="n">
-        <v>0.4599</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>0.6899</v>
+        <v>1.1675</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.23</v>
+        <v>-1.1675</v>
       </c>
     </row>
     <row r="16">
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.0245</v>
+        <v>1.4228</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.0555</v>
+        <v>-0.2698</v>
       </c>
       <c r="F16" t="n">
-        <v>1.08</v>
+        <v>1.6927</v>
       </c>
       <c r="G16" t="n">
         <v>-1.5219</v>
@@ -1702,13 +1702,13 @@
         <v>1.2487</v>
       </c>
       <c r="S16" t="n">
-        <v>0.0241</v>
+        <v>0.4224</v>
       </c>
       <c r="T16" t="n">
-        <v>0.4253</v>
+        <v>0.211</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.4012</v>
+        <v>0.2114</v>
       </c>
       <c r="V16" t="n">
         <v>1.2737</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>J. CERA RODRIGUEZ</t>
+          <t>A. MORALES ROS</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.8552</v>
+        <v>1.3033</v>
       </c>
       <c r="E17" t="n">
-        <v>1.3623</v>
+        <v>0.5795</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.5071</v>
+        <v>0.7238</v>
       </c>
       <c r="G17" t="n">
-        <v>1.8423</v>
+        <v>0.5607</v>
       </c>
       <c r="H17" t="n">
-        <v>0.0511</v>
+        <v>-0.4304</v>
       </c>
       <c r="I17" t="n">
-        <v>1.7912</v>
+        <v>0.9911</v>
       </c>
       <c r="J17" t="n">
-        <v>2.9937</v>
+        <v>1.3202</v>
       </c>
       <c r="K17" t="n">
-        <v>0.7779</v>
+        <v>0.1535</v>
       </c>
       <c r="L17" t="n">
-        <v>2.2158</v>
+        <v>1.1667</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.1513</v>
+        <v>-0.7595</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.7268</v>
+        <v>-0.5839</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.4245</v>
+        <v>-0.1755</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.4162</v>
+        <v>0.8325</v>
       </c>
       <c r="Q17" t="n">
-        <v>-2.0812</v>
+        <v>-1.0406</v>
       </c>
       <c r="R17" t="n">
-        <v>1.6649</v>
+        <v>1.8731</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.5708</v>
+        <v>-0.5498</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.7177</v>
+        <v>-0.39</v>
       </c>
       <c r="U17" t="n">
-        <v>0.1468</v>
+        <v>-0.1598</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>0.4599</v>
       </c>
       <c r="W17" t="n">
-        <v>1.1675</v>
+        <v>0.6899</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.1675</v>
+        <v>-0.23</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>O. SIMA FATTY</t>
+          <t>S. ROMERO SANCHEZ</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.1916</v>
+        <v>0.4372</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.6883</v>
+        <v>-1.2433</v>
       </c>
       <c r="F18" t="n">
-        <v>0.8799</v>
+        <v>1.6805</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.4489</v>
+        <v>-0.8557</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.7804</v>
+        <v>0.0407</v>
       </c>
       <c r="I18" t="n">
-        <v>0.3315</v>
+        <v>-0.8964</v>
       </c>
       <c r="J18" t="n">
-        <v>-1.2161</v>
+        <v>-1.0148</v>
       </c>
       <c r="K18" t="n">
-        <v>-1.2944</v>
+        <v>0.3838</v>
       </c>
       <c r="L18" t="n">
-        <v>0.0784</v>
+        <v>-1.3985</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.2328</v>
+        <v>0.1591</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.4859</v>
+        <v>-0.3431</v>
       </c>
       <c r="O18" t="n">
-        <v>0.2531</v>
+        <v>0.5021</v>
       </c>
       <c r="P18" t="n">
-        <v>1.0406</v>
+        <v>1.2487</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.0406</v>
+        <v>1.2487</v>
       </c>
       <c r="S18" t="n">
-        <v>0.8298</v>
+        <v>0.0442</v>
       </c>
       <c r="T18" t="n">
-        <v>0.5276999999999999</v>
+        <v>-0.2286</v>
       </c>
       <c r="U18" t="n">
-        <v>0.3021</v>
+        <v>0.2727</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.23</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.041</v>
+        <v>0.1775</v>
       </c>
       <c r="E19" t="n">
-        <v>0.3194</v>
+        <v>0.4266</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.2784</v>
+        <v>-0.2491</v>
       </c>
       <c r="G19" t="n">
         <v>0.1519</v>
@@ -1936,13 +1936,13 @@
         <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.1109</v>
+        <v>0.0256</v>
       </c>
       <c r="T19" t="n">
-        <v>0.0124</v>
+        <v>0.1195</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.1233</v>
+        <v>-0.0939</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>S. ROMERO SANCHEZ</t>
+          <t>O. SIMA FATTY</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.4852</v>
+        <v>-0.0125</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.9934</v>
+        <v>-1.0098</v>
       </c>
       <c r="F20" t="n">
-        <v>1.5083</v>
+        <v>0.9973</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.8557</v>
+        <v>-1.4489</v>
       </c>
       <c r="H20" t="n">
-        <v>0.0407</v>
+        <v>-1.7804</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.8964</v>
+        <v>0.3315</v>
       </c>
       <c r="J20" t="n">
-        <v>-1.0148</v>
+        <v>-1.2161</v>
       </c>
       <c r="K20" t="n">
-        <v>0.3838</v>
+        <v>-1.2944</v>
       </c>
       <c r="L20" t="n">
-        <v>-1.3985</v>
+        <v>0.0784</v>
       </c>
       <c r="M20" t="n">
-        <v>0.1591</v>
+        <v>-0.2328</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.3431</v>
+        <v>-0.4859</v>
       </c>
       <c r="O20" t="n">
-        <v>0.5021</v>
+        <v>0.2531</v>
       </c>
       <c r="P20" t="n">
-        <v>1.2487</v>
+        <v>1.0406</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.2487</v>
+        <v>1.0406</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.8781</v>
+        <v>0.6258</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.9786</v>
+        <v>0.2063</v>
       </c>
       <c r="U20" t="n">
-        <v>0.1005</v>
+        <v>0.4195</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>-0.23</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-0.23</v>
       </c>
     </row>
     <row r="21">
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>P. TREVIÑO QUINTILLÁ</t>
+          <t>N. OKEKE</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.5262</v>
+        <v>-1.3768</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.3216</v>
+        <v>0.4568</v>
       </c>
       <c r="F22" t="n">
-        <v>0.7954</v>
+        <v>-1.8335</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.8206</v>
+        <v>-1.6607</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.3389</v>
+        <v>-1.6077</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.4817</v>
+        <v>-0.0531</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.849</v>
+        <v>-0.5501</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.3306</v>
+        <v>-0.4929</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.5184</v>
+        <v>-0.0572</v>
       </c>
       <c r="M22" t="n">
-        <v>0.0284</v>
+        <v>-1.1106</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.0083</v>
+        <v>-1.1147</v>
       </c>
       <c r="O22" t="n">
-        <v>0.0367</v>
+        <v>0.0041</v>
       </c>
       <c r="P22" t="n">
+        <v>1.4568</v>
+      </c>
+      <c r="Q22" t="n">
         <v>-1.0406</v>
       </c>
-      <c r="Q22" t="n">
-        <v>-2.0812</v>
-      </c>
       <c r="R22" t="n">
-        <v>1.0406</v>
+        <v>2.4974</v>
       </c>
       <c r="S22" t="n">
-        <v>0.5649999999999999</v>
+        <v>-0.7129</v>
       </c>
       <c r="T22" t="n">
-        <v>0.6087</v>
+        <v>-0.2876</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.0437</v>
+        <v>-0.4253</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.23</v>
+        <v>-0.4599</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>2.3351</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.23</v>
+        <v>-2.795</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>N. OKEKE</t>
+          <t>P. TREVIÑO QUINTILLÁ</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.8617</v>
+        <v>-1.7596</v>
       </c>
       <c r="E23" t="n">
-        <v>0.3496</v>
+        <v>-2.643</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.2113</v>
+        <v>0.8835</v>
       </c>
       <c r="G23" t="n">
-        <v>-1.6607</v>
+        <v>-0.8206</v>
       </c>
       <c r="H23" t="n">
-        <v>-1.6077</v>
+        <v>-0.3389</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.0531</v>
+        <v>-0.4817</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.5501</v>
+        <v>-0.849</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.4929</v>
+        <v>-0.3306</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.0572</v>
+        <v>-0.5184</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.1106</v>
+        <v>0.0284</v>
       </c>
       <c r="N23" t="n">
-        <v>-1.1147</v>
+        <v>-0.0083</v>
       </c>
       <c r="O23" t="n">
-        <v>0.0041</v>
+        <v>0.0367</v>
       </c>
       <c r="P23" t="n">
-        <v>1.4568</v>
+        <v>-1.0406</v>
       </c>
       <c r="Q23" t="n">
-        <v>-1.0406</v>
+        <v>-2.0812</v>
       </c>
       <c r="R23" t="n">
-        <v>2.4974</v>
+        <v>1.0406</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.1978</v>
+        <v>0.3316</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.3948</v>
+        <v>0.2872</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.8031</v>
+        <v>0.0444</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.4599</v>
+        <v>-0.23</v>
       </c>
       <c r="W23" t="n">
-        <v>2.3351</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-2.795</v>
+        <v>-0.23</v>
       </c>
     </row>
     <row r="24">
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>14.47590000000001</v>
+        <v>15.1903</v>
       </c>
       <c r="E24" t="n">
-        <v>8.780800000000001</v>
+        <v>8.781100000000002</v>
       </c>
       <c r="F24" t="n">
-        <v>5.6952</v>
+        <v>6.4095</v>
       </c>
       <c r="G24" t="n">
         <v>2.714500000000001</v>
@@ -2296,28 +2296,28 @@
         <v>-3.3476</v>
       </c>
       <c r="I24" t="n">
-        <v>6.061899999999999</v>
+        <v>6.0619</v>
       </c>
       <c r="J24" t="n">
-        <v>8.472300000000001</v>
+        <v>8.472299999999999</v>
       </c>
       <c r="K24" t="n">
-        <v>2.2676</v>
+        <v>2.267599999999999</v>
       </c>
       <c r="L24" t="n">
-        <v>6.204900000000001</v>
+        <v>6.2049</v>
       </c>
       <c r="M24" t="n">
         <v>-5.7577</v>
       </c>
       <c r="N24" t="n">
-        <v>-5.6151</v>
+        <v>-5.615100000000001</v>
       </c>
       <c r="O24" t="n">
         <v>-0.1426999999999999</v>
       </c>
       <c r="P24" t="n">
-        <v>6.2435</v>
+        <v>6.243499999999999</v>
       </c>
       <c r="Q24" t="n">
         <v>-10.406</v>
@@ -2326,13 +2326,13 @@
         <v>16.6494</v>
       </c>
       <c r="S24" t="n">
-        <v>0.3883000000000001</v>
+        <v>1.1025</v>
       </c>
       <c r="T24" t="n">
         <v>-0.2354000000000001</v>
       </c>
       <c r="U24" t="n">
-        <v>0.6233999999999998</v>
+        <v>1.3379</v>
       </c>
       <c r="V24" t="n">
         <v>5.1301</v>
